--- a/shot-grid-frontend/docs/资产-样表.xlsx
+++ b/shot-grid-frontend/docs/资产-样表.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13335"/>
+    <workbookView windowWidth="28800" windowHeight="14055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>类型</t>
   </si>
@@ -55,9 +55,6 @@
     <t>状态</t>
   </si>
   <si>
-    <t>制作人</t>
-  </si>
-  <si>
     <t>场景</t>
   </si>
   <si>
@@ -70,13 +67,7 @@
     <t>翱天舱室内主视角</t>
   </si>
   <si>
-    <t>蒋浩</t>
-  </si>
-  <si>
     <t>翱天舱室内反打视角</t>
-  </si>
-  <si>
-    <t>嘉璋</t>
   </si>
   <si>
     <t>动力舱室内</t>
@@ -87,9 +78,6 @@
   </si>
   <si>
     <t>动力舱内正常气氛主视角</t>
-  </si>
-  <si>
-    <t>占峰</t>
   </si>
   <si>
     <t>动力舱恐怖气氛主视角</t>
@@ -184,9 +172,6 @@
     <t>角色三视图</t>
   </si>
   <si>
-    <t>蒋浩/春霞</t>
-  </si>
-  <si>
     <t>约瑟芬</t>
   </si>
   <si>
@@ -245,13 +230,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="黑体"/>
@@ -264,6 +242,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -621,7 +606,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -670,19 +655,6 @@
       <left style="thin">
         <color rgb="FF1F2329"/>
       </left>
-      <right style="thin">
-        <color rgb="FF1F2329"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF1F2329"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF1F2329"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FF1F2329"/>
       </right>
@@ -829,7 +801,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -841,34 +813,34 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -953,7 +925,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -963,37 +935,28 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1317,8 +1280,8 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultColWidth="12" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="12" defaultRowHeight="15.75" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -1326,12 +1289,9 @@
     <col min="4" max="4" width="37" customWidth="1"/>
     <col min="5" max="5" width="18.925" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="4" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:9">
+    <row r="1" ht="22.5" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1350,339 +1310,255 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:6">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3"/>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:9">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:6">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:6">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" ht="20" customHeight="1" spans="1:9">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:9">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:6">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:6">
+      <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5" t="s">
+      <c r="C6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:6">
+      <c r="A7" s="3"/>
+      <c r="B7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="1:9">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:9">
-      <c r="A6" s="4" t="s">
+      <c r="D7" s="4"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" ht="82" customHeight="1" spans="1:6">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:9">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5" t="s">
+      <c r="D8" s="4"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:6">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" ht="82" customHeight="1" spans="1:9">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" ht="20" customHeight="1" spans="1:9">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D10" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:9">
-      <c r="A10" s="4" t="s">
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:6">
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:6">
+      <c r="A12" s="3"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:6">
+      <c r="A13" s="3"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:6">
+      <c r="A14" s="3"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:9">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="5" t="s">
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:6">
+      <c r="A15" s="3"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:9">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="5" t="s">
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:6">
+      <c r="A16" s="3"/>
+      <c r="B16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:9">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:9">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" ht="20" customHeight="1" spans="1:9">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="5" t="s">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:6">
+      <c r="A17" s="3"/>
+      <c r="B17" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" ht="20" customHeight="1" spans="1:9">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:6">
+      <c r="A18" s="3"/>
+      <c r="B18" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" ht="20" customHeight="1" spans="1:8">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:6">
+      <c r="A19" s="3"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" ht="20" customHeight="1" spans="1:8">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5" t="s">
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:6">
+      <c r="A20" s="3"/>
+      <c r="B20" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C20" s="5"/>
+      <c r="D20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" ht="45" customHeight="1" spans="1:6">
+      <c r="A21" s="3"/>
+      <c r="B21" s="4">
+        <v>404</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" ht="20" customHeight="1" spans="1:8">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" ht="20" customHeight="1" spans="1:8">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" ht="45" customHeight="1" spans="1:8">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5">
-        <v>404</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="7"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I21" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F21" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="10">
